--- a/artfynd/A 61211-2024 artfynd.xlsx
+++ b/artfynd/A 61211-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2410,7 +2410,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112610394</v>
+        <v>112610397</v>
       </c>
       <c r="B17" t="n">
         <v>91048</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805889</v>
+        <v>805921</v>
       </c>
       <c r="R17" t="n">
-        <v>7354535</v>
+        <v>7354519</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112606740</v>
+        <v>112610395</v>
       </c>
       <c r="B18" t="n">
-        <v>91026</v>
+        <v>91024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,34 +2533,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805845</v>
+        <v>805904</v>
       </c>
       <c r="R18" t="n">
-        <v>7354566</v>
+        <v>7354531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112610397</v>
+        <v>112610390</v>
       </c>
       <c r="B19" t="n">
-        <v>91048</v>
+        <v>91026</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>805921</v>
+        <v>805846</v>
       </c>
       <c r="R19" t="n">
-        <v>7354519</v>
+        <v>7354564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,862 +2728,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112610395</v>
-      </c>
-      <c r="B20" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>805904</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7354531</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112606743</v>
-      </c>
-      <c r="B21" t="n">
-        <v>91048</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>805887</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7354532</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>112610390</v>
-      </c>
-      <c r="B22" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>805846</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7354564</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>112606744</v>
-      </c>
-      <c r="B23" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>805901</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7354536</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>112606742</v>
-      </c>
-      <c r="B24" t="n">
-        <v>91048</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>805891</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7354554</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>112606745</v>
-      </c>
-      <c r="B25" t="n">
-        <v>91048</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>805913</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7354518</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>112606739</v>
-      </c>
-      <c r="B26" t="n">
-        <v>91048</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>805871</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7354406</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>112606741</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>805891</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7354552</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61211-2024 artfynd.xlsx
+++ b/artfynd/A 61211-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104160188</v>
+        <v>112606739</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>805891.093830053</v>
+        <v>805871</v>
       </c>
       <c r="R2" t="n">
-        <v>7354554.457646813</v>
+        <v>7354406</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104160187</v>
+        <v>112606742</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>805890.9100555556</v>
+        <v>805891</v>
       </c>
       <c r="R3" t="n">
-        <v>7354552.399888512</v>
+        <v>7354554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104160190</v>
+        <v>112606743</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>805901.2207230008</v>
+        <v>805887</v>
       </c>
       <c r="R4" t="n">
-        <v>7354536.40636815</v>
+        <v>7354532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +947,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104160191</v>
+        <v>112606745</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>805913.4515794741</v>
+        <v>805913</v>
       </c>
       <c r="R5" t="n">
-        <v>7354517.769144915</v>
+        <v>7354518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,24 +1049,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,50 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104160186</v>
+        <v>112610393</v>
       </c>
       <c r="B6" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>805844.9857218107</v>
+        <v>805890</v>
       </c>
       <c r="R6" t="n">
-        <v>7354565.735700723</v>
+        <v>7354553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,24 +1151,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104160189</v>
+        <v>112610394</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1296,14 +1216,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>805887.3716685202</v>
+        <v>805889</v>
       </c>
       <c r="R7" t="n">
-        <v>7354532.452023549</v>
+        <v>7354535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,24 +1253,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,19 +1287,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104160185</v>
+        <v>112610397</v>
       </c>
       <c r="B8" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1413,14 +1318,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>805870.9621146189</v>
+        <v>805920</v>
       </c>
       <c r="R8" t="n">
-        <v>7354405.951310254</v>
+        <v>7354519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,24 +1355,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109910030</v>
+        <v>112606744</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,34 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>805887.0535179432</v>
+        <v>805901</v>
       </c>
       <c r="R9" t="n">
-        <v>7354550.349481497</v>
+        <v>7354536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,19 +1457,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1611,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109910032</v>
+        <v>112610395</v>
       </c>
       <c r="B10" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>805889.0805188955</v>
+        <v>805904</v>
       </c>
       <c r="R10" t="n">
-        <v>7354535.49106841</v>
+        <v>7354531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,19 +1559,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1728,50 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109910027</v>
+        <v>112606740</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>805846.0115353947</v>
+        <v>805845</v>
       </c>
       <c r="R11" t="n">
-        <v>7354563.809743274</v>
+        <v>7354566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,19 +1661,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1845,37 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109910036</v>
+        <v>112610390</v>
       </c>
       <c r="B12" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>805920.7094167918</v>
+        <v>805846</v>
       </c>
       <c r="R12" t="n">
-        <v>7354518.560040838</v>
+        <v>7354564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,19 +1763,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1962,19 +1797,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109910031</v>
+        <v>112606741</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1998,14 +1828,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>805889.971979473</v>
+        <v>805891</v>
       </c>
       <c r="R13" t="n">
-        <v>7354553.520312799</v>
+        <v>7354553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,19 +1865,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2079,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109910033</v>
+        <v>112610392</v>
       </c>
       <c r="B14" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>805904.210536551</v>
+        <v>805887</v>
       </c>
       <c r="R14" t="n">
-        <v>7354531.434010704</v>
+        <v>7354550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,19 +1967,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2193,541 +1998,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112610393</v>
-      </c>
-      <c r="B15" t="n">
-        <v>91048</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>805890</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7354554</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112610392</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>805887</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7354550</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112610397</v>
-      </c>
-      <c r="B17" t="n">
-        <v>91048</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>805921</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7354519</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112610395</v>
-      </c>
-      <c r="B18" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>805904</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7354531</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112610390</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Överstbyn, Nb</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>805846</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7354564</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61211-2024 artfynd.xlsx
+++ b/artfynd/A 61211-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606743</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606745</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610393</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610394</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610397</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606744</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610395</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606740</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610390</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606741</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,8 +2063,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610392</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>